--- a/data/historial_contactos.xlsx
+++ b/data/historial_contactos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I243"/>
+  <dimension ref="A1:I244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 13:44:36</t>
+          <t>2026-05-22T13:44:36+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 13:44:47</t>
+          <t>2026-05-22T13:44:47+00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,7 +560,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 13:45:03</t>
+          <t>2026-05-22T13:45:03+00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 13:45:28</t>
+          <t>2026-05-22T13:45:28+00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -654,7 +654,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-22 14:12:56</t>
+          <t>2026-05-22T14:12:56+00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -701,7 +701,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-22 14:13:42</t>
+          <t>2026-05-22T14:13:42+00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -748,7 +748,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-22 14:16:24</t>
+          <t>2026-05-22T14:16:24+00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -795,7 +795,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,7 +842,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -889,7 +889,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -936,7 +936,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -979,7 +979,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1026,7 +1026,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1069,7 +1069,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1112,7 +1112,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1331,7 +1331,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1374,7 +1374,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1460,7 +1460,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1503,7 +1503,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1546,7 +1546,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1589,7 +1589,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1632,7 +1632,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1675,7 +1675,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1718,7 +1718,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1804,7 +1804,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1847,7 +1847,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1890,7 +1890,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1933,7 +1933,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1976,7 +1976,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2062,7 +2062,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2105,7 +2105,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2148,7 +2148,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2191,7 +2191,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2234,7 +2234,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2277,7 +2277,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2320,7 +2320,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2363,7 +2363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2406,7 +2406,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2449,7 +2449,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2492,7 +2492,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2535,7 +2535,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2578,7 +2578,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2621,7 +2621,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2664,7 +2664,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2707,7 +2707,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2750,7 +2750,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2793,7 +2793,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2836,7 +2836,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2879,7 +2879,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2922,7 +2922,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2965,7 +2965,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3008,7 +3008,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3051,7 +3051,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3094,7 +3094,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3137,7 +3137,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3180,7 +3180,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3223,7 +3223,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3266,7 +3266,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3352,7 +3352,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3395,7 +3395,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3438,7 +3438,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3481,7 +3481,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3524,7 +3524,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3567,7 +3567,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3610,7 +3610,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3653,7 +3653,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3696,7 +3696,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3739,7 +3739,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3782,7 +3782,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3868,7 +3868,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3911,7 +3911,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3954,7 +3954,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3997,7 +3997,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4040,7 +4040,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4083,7 +4083,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4126,7 +4126,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4169,7 +4169,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4212,7 +4212,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4255,7 +4255,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4298,7 +4298,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4341,7 +4341,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4384,7 +4384,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4427,7 +4427,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4470,7 +4470,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4513,7 +4513,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4556,7 +4556,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4599,7 +4599,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4642,7 +4642,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4685,7 +4685,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4728,7 +4728,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4771,7 +4771,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4814,7 +4814,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4857,7 +4857,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4900,7 +4900,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4943,7 +4943,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4986,7 +4986,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5029,7 +5029,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5072,7 +5072,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5115,7 +5115,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5158,7 +5158,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5201,7 +5201,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5244,7 +5244,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5287,7 +5287,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5330,7 +5330,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5373,7 +5373,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5416,7 +5416,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5459,7 +5459,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5502,7 +5502,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5545,7 +5545,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5588,7 +5588,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5631,7 +5631,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5674,7 +5674,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5717,7 +5717,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5760,7 +5760,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5803,7 +5803,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5846,7 +5846,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5889,7 +5889,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5932,7 +5932,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5975,7 +5975,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6018,7 +6018,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6061,7 +6061,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6104,7 +6104,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6147,7 +6147,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6190,7 +6190,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6233,7 +6233,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6276,7 +6276,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6319,7 +6319,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6362,7 +6362,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6405,7 +6405,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6448,7 +6448,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6491,7 +6491,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6534,7 +6534,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6577,7 +6577,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6620,7 +6620,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6663,7 +6663,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6706,7 +6706,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6749,7 +6749,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6792,7 +6792,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6835,7 +6835,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6878,7 +6878,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6921,7 +6921,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6964,7 +6964,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -7007,7 +7007,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7050,7 +7050,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7093,7 +7093,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7136,7 +7136,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7179,7 +7179,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7222,7 +7222,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7265,7 +7265,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7308,7 +7308,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7351,7 +7351,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7394,7 +7394,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7437,7 +7437,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7480,7 +7480,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7523,7 +7523,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7566,7 +7566,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7609,7 +7609,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7652,7 +7652,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7695,7 +7695,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7738,7 +7738,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7781,7 +7781,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7824,7 +7824,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7867,7 +7867,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7910,7 +7910,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7953,7 +7953,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7996,7 +7996,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8039,7 +8039,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8082,7 +8082,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8125,7 +8125,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8168,7 +8168,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8211,7 +8211,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8254,7 +8254,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8297,7 +8297,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8340,7 +8340,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8383,7 +8383,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8426,7 +8426,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8469,7 +8469,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8512,7 +8512,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8555,7 +8555,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8598,7 +8598,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8641,7 +8641,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8684,7 +8684,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8727,7 +8727,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8770,7 +8770,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8813,7 +8813,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8856,7 +8856,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8899,7 +8899,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8942,7 +8942,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8985,7 +8985,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9028,7 +9028,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9071,7 +9071,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9114,7 +9114,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -9157,7 +9157,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -9200,7 +9200,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -9243,7 +9243,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -9286,7 +9286,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -9329,7 +9329,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -9372,7 +9372,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -9415,7 +9415,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -9458,7 +9458,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -9501,7 +9501,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -9544,7 +9544,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -9587,7 +9587,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -9630,7 +9630,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -9673,7 +9673,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -9716,7 +9716,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -9759,7 +9759,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -9802,7 +9802,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -9845,7 +9845,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -9888,7 +9888,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -9931,7 +9931,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -9974,7 +9974,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -10017,7 +10017,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -10060,7 +10060,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -10103,7 +10103,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -10146,7 +10146,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -10189,7 +10189,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -10232,7 +10232,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -10275,7 +10275,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -10318,7 +10318,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -10361,7 +10361,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -10404,7 +10404,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -10447,7 +10447,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -10490,7 +10490,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -10529,7 +10529,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-05-22 00:00:00</t>
+          <t>2026-05-22T00:00:00+00:00</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -10572,7 +10572,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-05-22 14:30:11</t>
+          <t>2026-05-22T14:30:11+00:00</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -10619,7 +10619,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-05-22 14:30:12</t>
+          <t>2026-05-22T14:30:12+00:00</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -10666,7 +10666,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-05-22 14:31:55</t>
+          <t>2026-05-22T14:31:55+00:00</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -10713,7 +10713,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-05-22 14:31:55</t>
+          <t>2026-05-22T14:31:55+00:00</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -10760,7 +10760,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-05-22 14:32:37</t>
+          <t>2026-05-22T14:32:37+00:00</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -10807,7 +10807,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-05-22 14:33:31</t>
+          <t>2026-05-22T14:33:31+00:00</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -10854,7 +10854,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-05-22 14:33:58</t>
+          <t>2026-05-22T14:33:58+00:00</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -10901,7 +10901,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-05-22 14:33:59</t>
+          <t>2026-05-22T14:33:59+00:00</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -10942,6 +10942,53 @@
       <c r="I243" t="inlineStr">
         <is>
           <t>hola</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:41:33</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Kechua+Vitacura/@-33.3817562,-70.57943,17z/data=!3m1!4b1!4m6!3m5!1s0x9662c91a55258adf:0x8b4d8fd1119ebaae!8m2!3d-33.3817562!4d-70.57943!16s%2Fg%2F11sj5dh_jm?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUxNy4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Kechua Vitacura</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Llamada</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Estado CRM cambiado</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Contactado</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Nuevo → Contactado</t>
         </is>
       </c>
     </row>
